--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.36274822527809</v>
+        <v>2.821446586607689</v>
       </c>
       <c r="D2" t="n">
-        <v>18.12047505319823</v>
+        <v>2.944577196144713</v>
       </c>
       <c r="E2" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F2" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.76753939624373</v>
+        <v>2.887225151889606</v>
       </c>
       <c r="D3" t="n">
-        <v>17.33195826324367</v>
+        <v>2.816443217777096</v>
       </c>
       <c r="E3" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F3" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.47320242061702</v>
+        <v>5.276895393350266</v>
       </c>
       <c r="D4" t="n">
-        <v>32.03054242561527</v>
+        <v>5.204963144162481</v>
       </c>
       <c r="E4" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F4" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.39947688063317</v>
+        <v>8.35241499310289</v>
       </c>
       <c r="D5" t="n">
-        <v>50.69462641520678</v>
+        <v>8.237876792471102</v>
       </c>
       <c r="E5" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F5" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.75822044956341</v>
+        <v>11.01071082305405</v>
       </c>
       <c r="D6" t="n">
-        <v>67.43988829792821</v>
+        <v>10.95898184841333</v>
       </c>
       <c r="E6" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F6" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.62900776667927</v>
+        <v>7.089713762085382</v>
       </c>
       <c r="D7" t="n">
-        <v>34.92224182373189</v>
+        <v>5.674864296356432</v>
       </c>
       <c r="E7" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F7" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.932784099744358</v>
+        <v>0.8015774162084582</v>
       </c>
       <c r="D8" t="n">
-        <v>4.796398869983656</v>
+        <v>0.7794148163723441</v>
       </c>
       <c r="E8" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F8" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>77.98508619273797</v>
+        <v>12.67257650631992</v>
       </c>
       <c r="D9" t="n">
-        <v>78.07337554559717</v>
+        <v>12.68692352615954</v>
       </c>
       <c r="E9" t="n">
-        <v>24.09355562902462</v>
+        <v>3.915202789716502</v>
       </c>
       <c r="F9" t="n">
-        <v>23.98864839254612</v>
+        <v>3.898155363788745</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
